--- a/xlsx/packagedata20260412-3 multitypepkg some stackable en.xlsx
+++ b/xlsx/packagedata20260412-3 multitypepkg some stackable en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8A125E-EFA0-474D-82AC-DEEE5A9B12F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BEF30-6749-46A0-A478-35AEECDAAA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t>pkg01</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,6 +115,10 @@
   </si>
   <si>
     <t>pkg03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双向可叉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,10 +481,13 @@
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.4140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5" customWidth="1"/>
+    <col min="9" max="9" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -695,8 +702,8 @@
       <c r="G6" t="s">
         <v>5</v>
       </c>
-      <c r="H6" t="s">
-        <v>4</v>
+      <c r="H6" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I6" t="s">
         <v>6</v>
@@ -704,7 +711,7 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="L6" t="s">
